--- a/docs/reports/WCR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
+++ b/docs/reports/WCR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,6 +309,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -857,19 +875,19 @@
         <f>'Daily Breakdown'!J212</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="46">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="47">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="48">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="47">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -877,19 +895,19 @@
         <f>'Daily Breakdown'!K212</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="46">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="47">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="47">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="48">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -939,7 +957,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1011,7 +1028,7 @@
       <c r="C4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="49" t="n">
         <v>541.66</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1051,7 +1068,7 @@
       <c r="C5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="49" t="n">
         <v>541.64</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1091,7 +1108,7 @@
       <c r="C6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="49" t="n">
         <v>543.63</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1131,7 +1148,7 @@
       <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="49" t="n">
         <v>543.64</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1171,7 +1188,7 @@
       <c r="C8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="49" t="n">
         <v>513.87</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1211,7 +1228,7 @@
       <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="49" t="n">
         <v>470.6</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1251,7 +1268,7 @@
       <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="49" t="n">
         <v>248.81</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1291,7 +1308,7 @@
       <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="49" t="n">
         <v>474.85</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1331,7 +1348,7 @@
       <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="49" t="n">
         <v>250.85</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1371,7 +1388,7 @@
       <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="49" t="n">
         <v>108.65</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1411,7 +1428,7 @@
       <c r="C14" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="49" t="n">
         <v>291.72</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1451,7 +1468,7 @@
       <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="49" t="n">
         <v>321.09</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1491,7 +1508,7 @@
       <c r="C16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="49" t="n">
         <v>329.43</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1531,7 +1548,7 @@
       <c r="C17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="49" t="n">
         <v>322.59</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1571,7 +1588,7 @@
       <c r="C18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1611,7 +1628,7 @@
       <c r="C19" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="49" t="n">
         <v>320.03</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1651,7 +1668,7 @@
       <c r="C20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="49" t="n">
         <v>328.19</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1691,7 +1708,7 @@
       <c r="C21" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="49" t="n">
         <v>222.33</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1731,7 +1748,7 @@
       <c r="C22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="49" t="n">
         <v>320.18</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1771,7 +1788,7 @@
       <c r="C23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="49" t="n">
         <v>322.06</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1811,7 +1828,7 @@
       <c r="C24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="49" t="n">
         <v>148</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1851,7 +1868,7 @@
       <c r="C25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="49" t="n">
         <v>107.79</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1891,7 +1908,7 @@
       <c r="C26" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="49" t="n">
         <v>108.53</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1931,7 +1948,7 @@
       <c r="C27" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="49" t="n">
         <v>222.34</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1971,7 +1988,7 @@
       <c r="C28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="49" t="n">
         <v>79.15000000000001</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2011,7 +2028,7 @@
       <c r="C29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="49" t="n">
         <v>8.93</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2051,7 +2068,7 @@
       <c r="C30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="49" t="n">
         <v>61.93</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2091,7 +2108,7 @@
       <c r="C31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="49" t="n">
         <v>214.59</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2131,7 +2148,7 @@
       <c r="C32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="49" t="n">
         <v>43.63</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2171,7 +2188,7 @@
       <c r="C33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="49" t="n">
         <v>143.06</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2211,7 +2228,7 @@
       <c r="C34" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="49" t="n">
         <v>57.83</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2251,7 +2268,7 @@
       <c r="C35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="49" t="n">
         <v>2.42</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2291,7 +2308,7 @@
       <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="49" t="n">
         <v>0.16</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2332,7 +2349,7 @@
         <f>SUM(C4:C36)</f>
         <v/>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="50">
         <f>SUM(D4:D36)</f>
         <v/>
       </c>
@@ -2379,7 +2396,7 @@
       <c r="C38" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="49" t="n">
         <v>543.66</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2419,7 +2436,7 @@
       <c r="C39" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="49" t="n">
         <v>543.86</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2459,7 +2476,7 @@
       <c r="C40" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="49" t="n">
         <v>541.63</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2499,7 +2516,7 @@
       <c r="C41" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="49" t="n">
         <v>541.66</v>
       </c>
       <c r="E41" s="18" t="n">
@@ -2539,7 +2556,7 @@
       <c r="C42" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="49" t="n">
         <v>541.48</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2579,7 +2596,7 @@
       <c r="C43" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="49" t="n">
         <v>252.17</v>
       </c>
       <c r="E43" s="18" t="n">
@@ -2619,7 +2636,7 @@
       <c r="C44" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E44" s="18" t="n">
@@ -2659,7 +2676,7 @@
       <c r="C45" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="49" t="n">
         <v>322.6</v>
       </c>
       <c r="E45" s="18" t="n">
@@ -2699,7 +2716,7 @@
       <c r="C46" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="49" t="n">
         <v>321.5</v>
       </c>
       <c r="E46" s="18" t="n">
@@ -2739,7 +2756,7 @@
       <c r="C47" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="49" t="n">
         <v>395.85</v>
       </c>
       <c r="E47" s="18" t="n">
@@ -2779,7 +2796,7 @@
       <c r="C48" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="49" t="n">
         <v>469.41</v>
       </c>
       <c r="E48" s="18" t="n">
@@ -2819,7 +2836,7 @@
       <c r="C49" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="49" t="n">
         <v>289.52</v>
       </c>
       <c r="E49" s="18" t="n">
@@ -2859,7 +2876,7 @@
       <c r="C50" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="49" t="n">
         <v>286.2</v>
       </c>
       <c r="E50" s="18" t="n">
@@ -2899,7 +2916,7 @@
       <c r="C51" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="49" t="n">
         <v>321.22</v>
       </c>
       <c r="E51" s="18" t="n">
@@ -2939,7 +2956,7 @@
       <c r="C52" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="49" t="n">
         <v>329.83</v>
       </c>
       <c r="E52" s="18" t="n">
@@ -2979,7 +2996,7 @@
       <c r="C53" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="49" t="n">
         <v>283.43</v>
       </c>
       <c r="E53" s="18" t="n">
@@ -3019,7 +3036,7 @@
       <c r="C54" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="49" t="n">
         <v>319.66</v>
       </c>
       <c r="E54" s="18" t="n">
@@ -3059,7 +3076,7 @@
       <c r="C55" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="49" t="n">
         <v>319.23</v>
       </c>
       <c r="E55" s="18" t="n">
@@ -3099,7 +3116,7 @@
       <c r="C56" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="17" t="n">
+      <c r="D56" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E56" s="18" t="n">
@@ -3139,7 +3156,7 @@
       <c r="C57" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D57" s="17" t="n">
+      <c r="D57" s="49" t="n">
         <v>321.42</v>
       </c>
       <c r="E57" s="18" t="n">
@@ -3179,7 +3196,7 @@
       <c r="C58" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="17" t="n">
+      <c r="D58" s="49" t="n">
         <v>108.54</v>
       </c>
       <c r="E58" s="18" t="n">
@@ -3219,7 +3236,7 @@
       <c r="C59" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="17" t="n">
+      <c r="D59" s="49" t="n">
         <v>318.81</v>
       </c>
       <c r="E59" s="18" t="n">
@@ -3259,7 +3276,7 @@
       <c r="C60" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="49" t="n">
         <v>246.67</v>
       </c>
       <c r="E60" s="18" t="n">
@@ -3299,7 +3316,7 @@
       <c r="C61" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="49" t="n">
         <v>215.87</v>
       </c>
       <c r="E61" s="18" t="n">
@@ -3339,7 +3356,7 @@
       <c r="C62" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="49" t="n">
         <v>148.55</v>
       </c>
       <c r="E62" s="18" t="n">
@@ -3379,7 +3396,7 @@
       <c r="C63" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="49" t="n">
         <v>60.27</v>
       </c>
       <c r="E63" s="18" t="n">
@@ -3419,7 +3436,7 @@
       <c r="C64" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="17" t="n">
+      <c r="D64" s="49" t="n">
         <v>75.89</v>
       </c>
       <c r="E64" s="18" t="n">
@@ -3460,7 +3477,7 @@
         <f>SUM(C38:C64)</f>
         <v/>
       </c>
-      <c r="D65" s="22">
+      <c r="D65" s="50">
         <f>SUM(D38:D64)</f>
         <v/>
       </c>
@@ -3507,7 +3524,7 @@
       <c r="C66" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D66" s="49" t="n">
         <v>543.86</v>
       </c>
       <c r="E66" s="18" t="n">
@@ -3547,7 +3564,7 @@
       <c r="C67" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="17" t="n">
+      <c r="D67" s="49" t="n">
         <v>541.64</v>
       </c>
       <c r="E67" s="18" t="n">
@@ -3587,7 +3604,7 @@
       <c r="C68" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D68" s="17" t="n">
+      <c r="D68" s="49" t="n">
         <v>543.85</v>
       </c>
       <c r="E68" s="18" t="n">
@@ -3627,7 +3644,7 @@
       <c r="C69" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D69" s="49" t="n">
         <v>542.92</v>
       </c>
       <c r="E69" s="18" t="n">
@@ -3667,7 +3684,7 @@
       <c r="C70" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D70" s="17" t="n">
+      <c r="D70" s="49" t="n">
         <v>251.9</v>
       </c>
       <c r="E70" s="18" t="n">
@@ -3707,7 +3724,7 @@
       <c r="C71" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D71" s="17" t="n">
+      <c r="D71" s="49" t="n">
         <v>329.83</v>
       </c>
       <c r="E71" s="18" t="n">
@@ -3747,7 +3764,7 @@
       <c r="C72" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D72" s="49" t="n">
         <v>184.38</v>
       </c>
       <c r="E72" s="18" t="n">
@@ -3787,7 +3804,7 @@
       <c r="C73" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="17" t="n">
+      <c r="D73" s="49" t="n">
         <v>469.41</v>
       </c>
       <c r="E73" s="18" t="n">
@@ -3827,7 +3844,7 @@
       <c r="C74" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D74" s="17" t="n">
+      <c r="D74" s="49" t="n">
         <v>483.52</v>
       </c>
       <c r="E74" s="18" t="n">
@@ -3867,7 +3884,7 @@
       <c r="C75" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="49" t="n">
         <v>473.4</v>
       </c>
       <c r="E75" s="18" t="n">
@@ -3907,7 +3924,7 @@
       <c r="C76" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D76" s="17" t="n">
+      <c r="D76" s="49" t="n">
         <v>470.59</v>
       </c>
       <c r="E76" s="18" t="n">
@@ -3947,7 +3964,7 @@
       <c r="C77" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D77" s="17" t="n">
+      <c r="D77" s="49" t="n">
         <v>322.4</v>
       </c>
       <c r="E77" s="18" t="n">
@@ -3987,7 +4004,7 @@
       <c r="C78" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="17" t="n">
+      <c r="D78" s="49" t="n">
         <v>392.7</v>
       </c>
       <c r="E78" s="18" t="n">
@@ -4027,7 +4044,7 @@
       <c r="C79" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="17" t="n">
+      <c r="D79" s="49" t="n">
         <v>167.36</v>
       </c>
       <c r="E79" s="18" t="n">
@@ -4067,7 +4084,7 @@
       <c r="C80" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D80" s="17" t="n">
+      <c r="D80" s="49" t="n">
         <v>254.36</v>
       </c>
       <c r="E80" s="18" t="n">
@@ -4107,7 +4124,7 @@
       <c r="C81" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="17" t="n">
+      <c r="D81" s="49" t="n">
         <v>329.92</v>
       </c>
       <c r="E81" s="18" t="n">
@@ -4147,7 +4164,7 @@
       <c r="C82" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="17" t="n">
+      <c r="D82" s="49" t="n">
         <v>319.22</v>
       </c>
       <c r="E82" s="18" t="n">
@@ -4187,7 +4204,7 @@
       <c r="C83" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D83" s="17" t="n">
+      <c r="D83" s="49" t="n">
         <v>318.79</v>
       </c>
       <c r="E83" s="18" t="n">
@@ -4227,7 +4244,7 @@
       <c r="C84" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D84" s="17" t="n">
+      <c r="D84" s="49" t="n">
         <v>319.21</v>
       </c>
       <c r="E84" s="18" t="n">
@@ -4267,7 +4284,7 @@
       <c r="C85" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D85" s="17" t="n">
+      <c r="D85" s="49" t="n">
         <v>108.54</v>
       </c>
       <c r="E85" s="18" t="n">
@@ -4307,7 +4324,7 @@
       <c r="C86" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D86" s="17" t="n">
+      <c r="D86" s="49" t="n">
         <v>108.51</v>
       </c>
       <c r="E86" s="18" t="n">
@@ -4347,7 +4364,7 @@
       <c r="C87" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D87" s="17" t="n">
+      <c r="D87" s="49" t="n">
         <v>190.05</v>
       </c>
       <c r="E87" s="18" t="n">
@@ -4387,7 +4404,7 @@
       <c r="C88" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D88" s="17" t="n">
+      <c r="D88" s="49" t="n">
         <v>170.97</v>
       </c>
       <c r="E88" s="18" t="n">
@@ -4427,7 +4444,7 @@
       <c r="C89" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="17" t="n">
+      <c r="D89" s="49" t="n">
         <v>165.44</v>
       </c>
       <c r="E89" s="18" t="n">
@@ -4467,7 +4484,7 @@
       <c r="C90" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D90" s="17" t="n">
+      <c r="D90" s="49" t="n">
         <v>322.41</v>
       </c>
       <c r="E90" s="18" t="n">
@@ -4507,7 +4524,7 @@
       <c r="C91" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="17" t="n">
+      <c r="D91" s="49" t="n">
         <v>0.82</v>
       </c>
       <c r="E91" s="18" t="n">
@@ -4547,7 +4564,7 @@
       <c r="C92" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D92" s="17" t="n">
+      <c r="D92" s="49" t="n">
         <v>57.71</v>
       </c>
       <c r="E92" s="18" t="n">
@@ -4587,7 +4604,7 @@
       <c r="C93" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D93" s="49" t="n">
         <v>36.91</v>
       </c>
       <c r="E93" s="18" t="n">
@@ -4628,7 +4645,7 @@
         <f>SUM(C66:C93)</f>
         <v/>
       </c>
-      <c r="D94" s="22">
+      <c r="D94" s="50">
         <f>SUM(D66:D93)</f>
         <v/>
       </c>
@@ -4675,7 +4692,7 @@
       <c r="C95" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D95" s="17" t="n">
+      <c r="D95" s="49" t="n">
         <v>543.87</v>
       </c>
       <c r="E95" s="18" t="n">
@@ -4715,7 +4732,7 @@
       <c r="C96" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D96" s="17" t="n">
+      <c r="D96" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E96" s="18" t="n">
@@ -4755,7 +4772,7 @@
       <c r="C97" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D97" s="17" t="n">
+      <c r="D97" s="49" t="n">
         <v>543.83</v>
       </c>
       <c r="E97" s="18" t="n">
@@ -4795,7 +4812,7 @@
       <c r="C98" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D98" s="17" t="n">
+      <c r="D98" s="49" t="n">
         <v>543.89</v>
       </c>
       <c r="E98" s="18" t="n">
@@ -4835,7 +4852,7 @@
       <c r="C99" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D99" s="17" t="n">
+      <c r="D99" s="49" t="n">
         <v>543.3200000000001</v>
       </c>
       <c r="E99" s="18" t="n">
@@ -4875,7 +4892,7 @@
       <c r="C100" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D100" s="17" t="n">
+      <c r="D100" s="49" t="n">
         <v>541.66</v>
       </c>
       <c r="E100" s="18" t="n">
@@ -4915,7 +4932,7 @@
       <c r="C101" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D101" s="17" t="n">
+      <c r="D101" s="49" t="n">
         <v>251.87</v>
       </c>
       <c r="E101" s="18" t="n">
@@ -4955,7 +4972,7 @@
       <c r="C102" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="17" t="n">
+      <c r="D102" s="49" t="n">
         <v>532.89</v>
       </c>
       <c r="E102" s="18" t="n">
@@ -4995,7 +5012,7 @@
       <c r="C103" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D103" s="17" t="n">
+      <c r="D103" s="49" t="n">
         <v>330.66</v>
       </c>
       <c r="E103" s="18" t="n">
@@ -5035,7 +5052,7 @@
       <c r="C104" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D104" s="17" t="n">
+      <c r="D104" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E104" s="18" t="n">
@@ -5075,7 +5092,7 @@
       <c r="C105" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="17" t="n">
+      <c r="D105" s="49" t="n">
         <v>376.46</v>
       </c>
       <c r="E105" s="18" t="n">
@@ -5115,7 +5132,7 @@
       <c r="C106" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D106" s="17" t="n">
+      <c r="D106" s="49" t="n">
         <v>109.14</v>
       </c>
       <c r="E106" s="18" t="n">
@@ -5155,7 +5172,7 @@
       <c r="C107" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="17" t="n">
+      <c r="D107" s="49" t="n">
         <v>329.1</v>
       </c>
       <c r="E107" s="18" t="n">
@@ -5195,7 +5212,7 @@
       <c r="C108" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="17" t="n">
+      <c r="D108" s="49" t="n">
         <v>318.79</v>
       </c>
       <c r="E108" s="18" t="n">
@@ -5235,7 +5252,7 @@
       <c r="C109" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="17" t="n">
+      <c r="D109" s="49" t="n">
         <v>240.77</v>
       </c>
       <c r="E109" s="18" t="n">
@@ -5275,7 +5292,7 @@
       <c r="C110" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="17" t="n">
+      <c r="D110" s="49" t="n">
         <v>321.7</v>
       </c>
       <c r="E110" s="18" t="n">
@@ -5315,7 +5332,7 @@
       <c r="C111" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="17" t="n">
+      <c r="D111" s="49" t="n">
         <v>108.43</v>
       </c>
       <c r="E111" s="18" t="n">
@@ -5355,7 +5372,7 @@
       <c r="C112" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="17" t="n">
+      <c r="D112" s="49" t="n">
         <v>319.2</v>
       </c>
       <c r="E112" s="18" t="n">
@@ -5395,7 +5412,7 @@
       <c r="C113" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="17" t="n">
+      <c r="D113" s="49" t="n">
         <v>222.31</v>
       </c>
       <c r="E113" s="18" t="n">
@@ -5435,7 +5452,7 @@
       <c r="C114" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="17" t="n">
+      <c r="D114" s="49" t="n">
         <v>164.16</v>
       </c>
       <c r="E114" s="18" t="n">
@@ -5475,7 +5492,7 @@
       <c r="C115" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="17" t="n">
+      <c r="D115" s="49" t="n">
         <v>106.8</v>
       </c>
       <c r="E115" s="18" t="n">
@@ -5515,7 +5532,7 @@
       <c r="C116" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="17" t="n">
+      <c r="D116" s="49" t="n">
         <v>66.36</v>
       </c>
       <c r="E116" s="18" t="n">
@@ -5555,7 +5572,7 @@
       <c r="C117" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="17" t="n">
+      <c r="D117" s="49" t="n">
         <v>44.24</v>
       </c>
       <c r="E117" s="18" t="n">
@@ -5595,7 +5612,7 @@
       <c r="C118" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="17" t="n">
+      <c r="D118" s="49" t="n">
         <v>81.45</v>
       </c>
       <c r="E118" s="18" t="n">
@@ -5635,7 +5652,7 @@
       <c r="C119" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="17" t="n">
+      <c r="D119" s="49" t="n">
         <v>17.63</v>
       </c>
       <c r="E119" s="18" t="n">
@@ -5675,7 +5692,7 @@
       <c r="C120" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="17" t="n">
+      <c r="D120" s="49" t="n">
         <v>3.64</v>
       </c>
       <c r="E120" s="18" t="n">
@@ -5715,7 +5732,7 @@
       <c r="C121" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="17" t="n">
+      <c r="D121" s="49" t="n">
         <v>292.92</v>
       </c>
       <c r="E121" s="18" t="n">
@@ -5756,7 +5773,7 @@
         <f>SUM(C95:C121)</f>
         <v/>
       </c>
-      <c r="D122" s="22">
+      <c r="D122" s="50">
         <f>SUM(D95:D121)</f>
         <v/>
       </c>
@@ -5803,7 +5820,7 @@
       <c r="C123" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D123" s="17" t="n">
+      <c r="D123" s="49" t="n">
         <v>543.8200000000001</v>
       </c>
       <c r="E123" s="18" t="n">
@@ -5843,7 +5860,7 @@
       <c r="C124" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D124" s="17" t="n">
+      <c r="D124" s="49" t="n">
         <v>543.64</v>
       </c>
       <c r="E124" s="18" t="n">
@@ -5883,7 +5900,7 @@
       <c r="C125" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="17" t="n">
+      <c r="D125" s="49" t="n">
         <v>252.17</v>
       </c>
       <c r="E125" s="18" t="n">
@@ -5923,7 +5940,7 @@
       <c r="C126" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="17" t="n">
+      <c r="D126" s="49" t="n">
         <v>526.3</v>
       </c>
       <c r="E126" s="18" t="n">
@@ -5963,7 +5980,7 @@
       <c r="C127" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D127" s="17" t="n">
+      <c r="D127" s="49" t="n">
         <v>320.19</v>
       </c>
       <c r="E127" s="18" t="n">
@@ -6003,7 +6020,7 @@
       <c r="C128" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="17" t="n">
+      <c r="D128" s="49" t="n">
         <v>475.26</v>
       </c>
       <c r="E128" s="18" t="n">
@@ -6043,7 +6060,7 @@
       <c r="C129" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D129" s="17" t="n">
+      <c r="D129" s="49" t="n">
         <v>474.04</v>
       </c>
       <c r="E129" s="18" t="n">
@@ -6083,7 +6100,7 @@
       <c r="C130" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D130" s="17" t="n">
+      <c r="D130" s="49" t="n">
         <v>472.22</v>
       </c>
       <c r="E130" s="18" t="n">
@@ -6123,7 +6140,7 @@
       <c r="C131" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="17" t="n">
+      <c r="D131" s="49" t="n">
         <v>329.83</v>
       </c>
       <c r="E131" s="18" t="n">
@@ -6163,7 +6180,7 @@
       <c r="C132" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D132" s="17" t="n">
+      <c r="D132" s="49" t="n">
         <v>322.6</v>
       </c>
       <c r="E132" s="18" t="n">
@@ -6203,7 +6220,7 @@
       <c r="C133" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D133" s="17" t="n">
+      <c r="D133" s="49" t="n">
         <v>321.72</v>
       </c>
       <c r="E133" s="18" t="n">
@@ -6243,7 +6260,7 @@
       <c r="C134" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="17" t="n">
+      <c r="D134" s="49" t="n">
         <v>108.53</v>
       </c>
       <c r="E134" s="18" t="n">
@@ -6283,7 +6300,7 @@
       <c r="C135" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D135" s="17" t="n">
+      <c r="D135" s="49" t="n">
         <v>322.16</v>
       </c>
       <c r="E135" s="18" t="n">
@@ -6323,7 +6340,7 @@
       <c r="C136" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D136" s="17" t="n">
+      <c r="D136" s="49" t="n">
         <v>321.37</v>
       </c>
       <c r="E136" s="18" t="n">
@@ -6363,7 +6380,7 @@
       <c r="C137" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D137" s="17" t="n">
+      <c r="D137" s="49" t="n">
         <v>261.38</v>
       </c>
       <c r="E137" s="18" t="n">
@@ -6403,7 +6420,7 @@
       <c r="C138" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D138" s="17" t="n">
+      <c r="D138" s="49" t="n">
         <v>233.63</v>
       </c>
       <c r="E138" s="18" t="n">
@@ -6443,7 +6460,7 @@
       <c r="C139" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D139" s="17" t="n">
+      <c r="D139" s="49" t="n">
         <v>108.01</v>
       </c>
       <c r="E139" s="18" t="n">
@@ -6483,7 +6500,7 @@
       <c r="C140" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D140" s="17" t="n">
+      <c r="D140" s="49" t="n">
         <v>300.88</v>
       </c>
       <c r="E140" s="18" t="n">
@@ -6523,7 +6540,7 @@
       <c r="C141" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D141" s="17" t="n">
+      <c r="D141" s="49" t="n">
         <v>319.09</v>
       </c>
       <c r="E141" s="18" t="n">
@@ -6563,7 +6580,7 @@
       <c r="C142" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D142" s="17" t="n">
+      <c r="D142" s="49" t="n">
         <v>107.63</v>
       </c>
       <c r="E142" s="18" t="n">
@@ -6603,7 +6620,7 @@
       <c r="C143" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D143" s="17" t="n">
+      <c r="D143" s="49" t="n">
         <v>117.85</v>
       </c>
       <c r="E143" s="18" t="n">
@@ -6643,7 +6660,7 @@
       <c r="C144" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D144" s="17" t="n">
+      <c r="D144" s="49" t="n">
         <v>277.73</v>
       </c>
       <c r="E144" s="18" t="n">
@@ -6683,7 +6700,7 @@
       <c r="C145" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D145" s="17" t="n">
+      <c r="D145" s="49" t="n">
         <v>327.14</v>
       </c>
       <c r="E145" s="18" t="n">
@@ -6723,7 +6740,7 @@
       <c r="C146" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D146" s="17" t="n">
+      <c r="D146" s="49" t="n">
         <v>45.11</v>
       </c>
       <c r="E146" s="18" t="n">
@@ -6763,7 +6780,7 @@
       <c r="C147" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D147" s="17" t="n">
+      <c r="D147" s="49" t="n">
         <v>65.53</v>
       </c>
       <c r="E147" s="18" t="n">
@@ -6803,7 +6820,7 @@
       <c r="C148" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D148" s="17" t="n">
+      <c r="D148" s="49" t="n">
         <v>0.2</v>
       </c>
       <c r="E148" s="18" t="n">
@@ -6843,7 +6860,7 @@
       <c r="C149" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D149" s="17" t="n">
+      <c r="D149" s="49" t="n">
         <v>4.09</v>
       </c>
       <c r="E149" s="18" t="n">
@@ -6883,7 +6900,7 @@
       <c r="C150" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D150" s="17" t="n">
+      <c r="D150" s="49" t="n">
         <v>320.98</v>
       </c>
       <c r="E150" s="18" t="n">
@@ -6924,7 +6941,7 @@
         <f>SUM(C123:C150)</f>
         <v/>
       </c>
-      <c r="D151" s="22">
+      <c r="D151" s="50">
         <f>SUM(D123:D150)</f>
         <v/>
       </c>
@@ -6971,7 +6988,7 @@
       <c r="C152" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D152" s="17" t="n">
+      <c r="D152" s="49" t="n">
         <v>543.9</v>
       </c>
       <c r="E152" s="18" t="n">
@@ -7011,7 +7028,7 @@
       <c r="C153" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D153" s="17" t="n">
+      <c r="D153" s="49" t="n">
         <v>541.28</v>
       </c>
       <c r="E153" s="18" t="n">
@@ -7051,7 +7068,7 @@
       <c r="C154" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D154" s="17" t="n">
+      <c r="D154" s="49" t="n">
         <v>541.62</v>
       </c>
       <c r="E154" s="18" t="n">
@@ -7091,7 +7108,7 @@
       <c r="C155" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D155" s="17" t="n">
+      <c r="D155" s="49" t="n">
         <v>541.62</v>
       </c>
       <c r="E155" s="18" t="n">
@@ -7131,7 +7148,7 @@
       <c r="C156" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D156" s="17" t="n">
+      <c r="D156" s="49" t="n">
         <v>541.5</v>
       </c>
       <c r="E156" s="18" t="n">
@@ -7171,7 +7188,7 @@
       <c r="C157" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D157" s="17" t="n">
+      <c r="D157" s="49" t="n">
         <v>543.89</v>
       </c>
       <c r="E157" s="18" t="n">
@@ -7211,7 +7228,7 @@
       <c r="C158" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D158" s="17" t="n">
+      <c r="D158" s="49" t="n">
         <v>251.84</v>
       </c>
       <c r="E158" s="18" t="n">
@@ -7251,7 +7268,7 @@
       <c r="C159" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D159" s="17" t="n">
+      <c r="D159" s="49" t="n">
         <v>321.5</v>
       </c>
       <c r="E159" s="18" t="n">
@@ -7291,7 +7308,7 @@
       <c r="C160" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D160" s="17" t="n">
+      <c r="D160" s="49" t="n">
         <v>470.59</v>
       </c>
       <c r="E160" s="18" t="n">
@@ -7331,7 +7348,7 @@
       <c r="C161" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D161" s="17" t="n">
+      <c r="D161" s="49" t="n">
         <v>329.84</v>
       </c>
       <c r="E161" s="18" t="n">
@@ -7371,7 +7388,7 @@
       <c r="C162" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D162" s="17" t="n">
+      <c r="D162" s="49" t="n">
         <v>471.86</v>
       </c>
       <c r="E162" s="18" t="n">
@@ -7411,7 +7428,7 @@
       <c r="C163" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D163" s="17" t="n">
+      <c r="D163" s="49" t="n">
         <v>332.64</v>
       </c>
       <c r="E163" s="18" t="n">
@@ -7451,7 +7468,7 @@
       <c r="C164" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D164" s="17" t="n">
+      <c r="D164" s="49" t="n">
         <v>321.72</v>
       </c>
       <c r="E164" s="18" t="n">
@@ -7491,7 +7508,7 @@
       <c r="C165" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D165" s="17" t="n">
+      <c r="D165" s="49" t="n">
         <v>273.7</v>
       </c>
       <c r="E165" s="18" t="n">
@@ -7531,7 +7548,7 @@
       <c r="C166" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D166" s="17" t="n">
+      <c r="D166" s="49" t="n">
         <v>318.8</v>
       </c>
       <c r="E166" s="18" t="n">
@@ -7571,7 +7588,7 @@
       <c r="C167" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D167" s="17" t="n">
+      <c r="D167" s="49" t="n">
         <v>248.69</v>
       </c>
       <c r="E167" s="18" t="n">
@@ -7611,7 +7628,7 @@
       <c r="C168" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D168" s="17" t="n">
+      <c r="D168" s="49" t="n">
         <v>319.22</v>
       </c>
       <c r="E168" s="18" t="n">
@@ -7651,7 +7668,7 @@
       <c r="C169" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D169" s="17" t="n">
+      <c r="D169" s="49" t="n">
         <v>107.95</v>
       </c>
       <c r="E169" s="18" t="n">
@@ -7691,7 +7708,7 @@
       <c r="C170" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D170" s="17" t="n">
+      <c r="D170" s="49" t="n">
         <v>161.31</v>
       </c>
       <c r="E170" s="18" t="n">
@@ -7731,7 +7748,7 @@
       <c r="C171" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D171" s="17" t="n">
+      <c r="D171" s="49" t="n">
         <v>248.18</v>
       </c>
       <c r="E171" s="18" t="n">
@@ -7771,7 +7788,7 @@
       <c r="C172" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D172" s="17" t="n">
+      <c r="D172" s="49" t="n">
         <v>87.51000000000001</v>
       </c>
       <c r="E172" s="18" t="n">
@@ -7811,7 +7828,7 @@
       <c r="C173" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D173" s="17" t="n">
+      <c r="D173" s="49" t="n">
         <v>107.84</v>
       </c>
       <c r="E173" s="18" t="n">
@@ -7851,7 +7868,7 @@
       <c r="C174" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D174" s="17" t="n">
+      <c r="D174" s="49" t="n">
         <v>88.8</v>
       </c>
       <c r="E174" s="18" t="n">
@@ -7891,7 +7908,7 @@
       <c r="C175" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D175" s="17" t="n">
+      <c r="D175" s="49" t="n">
         <v>67.56999999999999</v>
       </c>
       <c r="E175" s="18" t="n">
@@ -7931,7 +7948,7 @@
       <c r="C176" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D176" s="17" t="n">
+      <c r="D176" s="49" t="n">
         <v>41.04</v>
       </c>
       <c r="E176" s="18" t="n">
@@ -7971,7 +7988,7 @@
       <c r="C177" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D177" s="17" t="n">
+      <c r="D177" s="49" t="n">
         <v>40.18</v>
       </c>
       <c r="E177" s="18" t="n">
@@ -8011,7 +8028,7 @@
       <c r="C178" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D178" s="17" t="n">
+      <c r="D178" s="49" t="n">
         <v>0.78</v>
       </c>
       <c r="E178" s="18" t="n">
@@ -8052,7 +8069,7 @@
         <f>SUM(C152:C178)</f>
         <v/>
       </c>
-      <c r="D179" s="22">
+      <c r="D179" s="50">
         <f>SUM(D152:D178)</f>
         <v/>
       </c>
@@ -8099,7 +8116,7 @@
       <c r="C180" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D180" s="17" t="n">
+      <c r="D180" s="49" t="n">
         <v>543.88</v>
       </c>
       <c r="E180" s="18" t="n">
@@ -8139,7 +8156,7 @@
       <c r="C181" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D181" s="17" t="n">
+      <c r="D181" s="49" t="n">
         <v>541.62</v>
       </c>
       <c r="E181" s="18" t="n">
@@ -8179,7 +8196,7 @@
       <c r="C182" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D182" s="17" t="n">
+      <c r="D182" s="49" t="n">
         <v>543.85</v>
       </c>
       <c r="E182" s="18" t="n">
@@ -8219,7 +8236,7 @@
       <c r="C183" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D183" s="17" t="n">
+      <c r="D183" s="49" t="n">
         <v>543.13</v>
       </c>
       <c r="E183" s="18" t="n">
@@ -8259,7 +8276,7 @@
       <c r="C184" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D184" s="17" t="n">
+      <c r="D184" s="49" t="n">
         <v>536.78</v>
       </c>
       <c r="E184" s="18" t="n">
@@ -8299,7 +8316,7 @@
       <c r="C185" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D185" s="17" t="n">
+      <c r="D185" s="49" t="n">
         <v>251.78</v>
       </c>
       <c r="E185" s="18" t="n">
@@ -8339,7 +8356,7 @@
       <c r="C186" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D186" s="17" t="n">
+      <c r="D186" s="49" t="n">
         <v>180.69</v>
       </c>
       <c r="E186" s="18" t="n">
@@ -8379,7 +8396,7 @@
       <c r="C187" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D187" s="17" t="n">
+      <c r="D187" s="49" t="n">
         <v>321.5</v>
       </c>
       <c r="E187" s="18" t="n">
@@ -8419,7 +8436,7 @@
       <c r="C188" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D188" s="17" t="n">
+      <c r="D188" s="49" t="n">
         <v>454.12</v>
       </c>
       <c r="E188" s="18" t="n">
@@ -8459,7 +8476,7 @@
       <c r="C189" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D189" s="17" t="n">
+      <c r="D189" s="49" t="n">
         <v>392.7</v>
       </c>
       <c r="E189" s="18" t="n">
@@ -8499,7 +8516,7 @@
       <c r="C190" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="17" t="n">
+      <c r="D190" s="49" t="n">
         <v>470.58</v>
       </c>
       <c r="E190" s="18" t="n">
@@ -8539,7 +8556,7 @@
       <c r="C191" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D191" s="17" t="n">
+      <c r="D191" s="49" t="n">
         <v>473.5</v>
       </c>
       <c r="E191" s="18" t="n">
@@ -8579,7 +8596,7 @@
       <c r="C192" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D192" s="17" t="n">
+      <c r="D192" s="49" t="n">
         <v>289.66</v>
       </c>
       <c r="E192" s="18" t="n">
@@ -8619,7 +8636,7 @@
       <c r="C193" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D193" s="17" t="n">
+      <c r="D193" s="49" t="n">
         <v>476.08</v>
       </c>
       <c r="E193" s="18" t="n">
@@ -8659,7 +8676,7 @@
       <c r="C194" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D194" s="17" t="n">
+      <c r="D194" s="49" t="n">
         <v>320.03</v>
       </c>
       <c r="E194" s="18" t="n">
@@ -8699,7 +8716,7 @@
       <c r="C195" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D195" s="17" t="n">
+      <c r="D195" s="49" t="n">
         <v>330.69</v>
       </c>
       <c r="E195" s="18" t="n">
@@ -8739,7 +8756,7 @@
       <c r="C196" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D196" s="17" t="n">
+      <c r="D196" s="49" t="n">
         <v>321.71</v>
       </c>
       <c r="E196" s="18" t="n">
@@ -8779,7 +8796,7 @@
       <c r="C197" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D197" s="17" t="n">
+      <c r="D197" s="49" t="n">
         <v>180.75</v>
       </c>
       <c r="E197" s="18" t="n">
@@ -8819,7 +8836,7 @@
       <c r="C198" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D198" s="17" t="n">
+      <c r="D198" s="49" t="n">
         <v>319.23</v>
       </c>
       <c r="E198" s="18" t="n">
@@ -8859,7 +8876,7 @@
       <c r="C199" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D199" s="17" t="n">
+      <c r="D199" s="49" t="n">
         <v>233.18</v>
       </c>
       <c r="E199" s="18" t="n">
@@ -8899,7 +8916,7 @@
       <c r="C200" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D200" s="17" t="n">
+      <c r="D200" s="49" t="n">
         <v>211.29</v>
       </c>
       <c r="E200" s="18" t="n">
@@ -8939,7 +8956,7 @@
       <c r="C201" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D201" s="17" t="n">
+      <c r="D201" s="49" t="n">
         <v>235.19</v>
       </c>
       <c r="E201" s="18" t="n">
@@ -8979,7 +8996,7 @@
       <c r="C202" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D202" s="17" t="n">
+      <c r="D202" s="49" t="n">
         <v>292.96</v>
       </c>
       <c r="E202" s="18" t="n">
@@ -9019,7 +9036,7 @@
       <c r="C203" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D203" s="17" t="n">
+      <c r="D203" s="49" t="n">
         <v>167.72</v>
       </c>
       <c r="E203" s="18" t="n">
@@ -9059,7 +9076,7 @@
       <c r="C204" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D204" s="17" t="n">
+      <c r="D204" s="49" t="n">
         <v>168.19</v>
       </c>
       <c r="E204" s="18" t="n">
@@ -9099,7 +9116,7 @@
       <c r="C205" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D205" s="17" t="n">
+      <c r="D205" s="49" t="n">
         <v>208.11</v>
       </c>
       <c r="E205" s="18" t="n">
@@ -9139,7 +9156,7 @@
       <c r="C206" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D206" s="17" t="n">
+      <c r="D206" s="49" t="n">
         <v>106.73</v>
       </c>
       <c r="E206" s="18" t="n">
@@ -9179,7 +9196,7 @@
       <c r="C207" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D207" s="17" t="n">
+      <c r="D207" s="49" t="n">
         <v>127.28</v>
       </c>
       <c r="E207" s="18" t="n">
@@ -9219,7 +9236,7 @@
       <c r="C208" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D208" s="17" t="n">
+      <c r="D208" s="49" t="n">
         <v>49.72</v>
       </c>
       <c r="E208" s="18" t="n">
@@ -9259,7 +9276,7 @@
       <c r="C209" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D209" s="17" t="n">
+      <c r="D209" s="49" t="n">
         <v>5.92</v>
       </c>
       <c r="E209" s="18" t="n">
@@ -9299,7 +9316,7 @@
       <c r="C210" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D210" s="17" t="n">
+      <c r="D210" s="49" t="n">
         <v>0.95</v>
       </c>
       <c r="E210" s="18" t="n">
@@ -9340,7 +9357,7 @@
         <f>SUM(C180:C210)</f>
         <v/>
       </c>
-      <c r="D211" s="22">
+      <c r="D211" s="50">
         <f>SUM(D180:D210)</f>
         <v/>
       </c>
@@ -9384,7 +9401,7 @@
         <f>C37+C65+C94+C122+C151+C179+C211</f>
         <v/>
       </c>
-      <c r="D212" s="27">
+      <c r="D212" s="51">
         <f>D37+D65+D94+D122+D151+D179+D211</f>
         <v/>
       </c>
@@ -11187,7 +11204,7 @@
       </c>
       <c r="P23" s="34" t="inlineStr">
         <is>
-          <t>EB at 0-1 km/h (Standby)</t>
+          <t>EB at 0-1 km/h; StandBy Mode</t>
         </is>
       </c>
       <c r="Q23" s="33" t="inlineStr">
@@ -58178,7 +58195,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -77520,7 +77536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -77535,7 +77551,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="44" t="inlineStr">
         <is>

--- a/docs/reports/WCR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
+++ b/docs/reports/WCR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
@@ -732,7 +732,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -957,6 +956,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2358,7 +2364,7 @@
         <v/>
       </c>
       <c r="F37" s="23">
-        <f>SUM(F4:F36)</f>
+        <f>SUMIF(E4:E36,"&gt;0",F4:F36)</f>
         <v/>
       </c>
       <c r="G37" s="24">
@@ -3486,7 +3492,7 @@
         <v/>
       </c>
       <c r="F65" s="23">
-        <f>SUM(F38:F64)</f>
+        <f>SUMIF(E38:E64,"&gt;0",F38:F64)</f>
         <v/>
       </c>
       <c r="G65" s="24">
@@ -4654,7 +4660,7 @@
         <v/>
       </c>
       <c r="F94" s="23">
-        <f>SUM(F66:F93)</f>
+        <f>SUMIF(E66:E93,"&gt;0",F66:F93)</f>
         <v/>
       </c>
       <c r="G94" s="24">
@@ -5782,7 +5788,7 @@
         <v/>
       </c>
       <c r="F122" s="23">
-        <f>SUM(F95:F121)</f>
+        <f>SUMIF(E95:E121,"&gt;0",F95:F121)</f>
         <v/>
       </c>
       <c r="G122" s="24">
@@ -6950,7 +6956,7 @@
         <v/>
       </c>
       <c r="F151" s="23">
-        <f>SUM(F123:F150)</f>
+        <f>SUMIF(E123:E150,"&gt;0",F123:F150)</f>
         <v/>
       </c>
       <c r="G151" s="24">
@@ -8078,7 +8084,7 @@
         <v/>
       </c>
       <c r="F179" s="23">
-        <f>SUM(F152:F178)</f>
+        <f>SUMIF(E152:E178,"&gt;0",F152:F178)</f>
         <v/>
       </c>
       <c r="G179" s="24">
@@ -9366,7 +9372,7 @@
         <v/>
       </c>
       <c r="F211" s="23">
-        <f>SUM(F180:F210)</f>
+        <f>SUMIF(E180:E210,"&gt;0",F180:F210)</f>
         <v/>
       </c>
       <c r="G211" s="24">
@@ -9479,7 +9485,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -9487,7 +9492,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
